--- a/output/pdf_financials_xlsx/HYLQ.xlsx
+++ b/output/pdf_financials_xlsx/HYLQ.xlsx
@@ -2277,16 +2277,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.034782</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.034782</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.319456</v>
+        <v>3.885844</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.691943</v>
+        <v>5.709636</v>
       </c>
     </row>
     <row r="93">
@@ -3640,7 +3640,11 @@
           <t>Warrants reserve 15</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3990,7 +3994,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -4024,7 +4032,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4164,7 +4176,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>1.512516</v>
       </c>
@@ -4198,7 +4214,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.522266</v>
       </c>

--- a/output/pdf_financials_xlsx/HYLQ.xlsx
+++ b/output/pdf_financials_xlsx/HYLQ.xlsx
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.357453</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.767256</v>
+        <v>2.260263</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.869844</v>
+        <v>1.033556</v>
       </c>
     </row>
     <row r="11">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.357453</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.845498</v>
+        <v>-1.00921</v>
       </c>
     </row>
     <row r="12">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">

--- a/output/pdf_financials_xlsx/HYLQ.xlsx
+++ b/output/pdf_financials_xlsx/HYLQ.xlsx
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.06387900000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.039023</v>
+        <v>0.124023</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.004114</v>
+        <v>0.125911</v>
       </c>
     </row>
     <row r="8">
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.442791</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.214564</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.5381</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.134663</v>
       </c>
     </row>
     <row r="68">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.866955</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -6168,7 +6168,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>0.866955</v>
       </c>
@@ -6314,7 +6318,11 @@
           <t>Director fees 18</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -6992,7 +7000,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
